--- a/artfynd/A 5863-2026 artfynd.xlsx
+++ b/artfynd/A 5863-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ34"/>
+  <dimension ref="A1:AZ36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4518,6 +4518,246 @@
       <c r="AZ34" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/134624677</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>137176994</v>
+      </c>
+      <c r="B35" t="n">
+        <v>43500</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>101242</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Dårgräsfjäril</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Lopinga achine</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Scopoli, 1763)</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>5. Väntinge skogsbilväg, Gtl</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>699791</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6365700</v>
+      </c>
+      <c r="S35" t="n">
+        <v>5</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Hejde</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF35" t="inlineStr"/>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Arne Pettersson</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Arne Pettersson</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr">
+        <is>
+          <t>Biogeografisk uppföljning av fjärilar</t>
+        </is>
+      </c>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137176994</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>137177000</v>
+      </c>
+      <c r="B36" t="n">
+        <v>43500</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>101242</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Dårgräsfjäril</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Lopinga achine</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Scopoli, 1763)</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>5. Väntinge skogsbilväg, Gtl</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>699784</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6365713</v>
+      </c>
+      <c r="S36" t="n">
+        <v>5</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Hejde</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF36" t="inlineStr"/>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Arne Pettersson</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Arne Pettersson</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr">
+        <is>
+          <t>Biogeografisk uppföljning av fjärilar</t>
+        </is>
+      </c>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137177000</t>
         </is>
       </c>
     </row>
@@ -4556,6 +4796,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 5863-2026 artfynd.xlsx
+++ b/artfynd/A 5863-2026 artfynd.xlsx
@@ -4526,7 +4526,7 @@
         <v>137176994</v>
       </c>
       <c r="B35" t="n">
-        <v>43500</v>
+        <v>43513</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4646,7 +4646,7 @@
         <v>137177000</v>
       </c>
       <c r="B36" t="n">
-        <v>43500</v>
+        <v>43513</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>

--- a/artfynd/A 5863-2026 artfynd.xlsx
+++ b/artfynd/A 5863-2026 artfynd.xlsx
@@ -4526,7 +4526,7 @@
         <v>137176994</v>
       </c>
       <c r="B35" t="n">
-        <v>43513</v>
+        <v>43515</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4646,7 +4646,7 @@
         <v>137177000</v>
       </c>
       <c r="B36" t="n">
-        <v>43513</v>
+        <v>43515</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>

--- a/artfynd/A 5863-2026 artfynd.xlsx
+++ b/artfynd/A 5863-2026 artfynd.xlsx
@@ -4557,11 +4557,7 @@
         </is>
       </c>
       <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
+      <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr"/>
       <c r="M35" t="inlineStr"/>
       <c r="N35" t="inlineStr"/>
@@ -4677,11 +4673,7 @@
         </is>
       </c>
       <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
+      <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr"/>
       <c r="M36" t="inlineStr"/>
       <c r="N36" t="inlineStr"/>

--- a/artfynd/A 5863-2026 artfynd.xlsx
+++ b/artfynd/A 5863-2026 artfynd.xlsx
@@ -4526,7 +4526,7 @@
         <v>137176994</v>
       </c>
       <c r="B35" t="n">
-        <v>43515</v>
+        <v>43525</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4642,7 +4642,7 @@
         <v>137177000</v>
       </c>
       <c r="B36" t="n">
-        <v>43515</v>
+        <v>43525</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>

--- a/artfynd/A 5863-2026 artfynd.xlsx
+++ b/artfynd/A 5863-2026 artfynd.xlsx
@@ -4526,7 +4526,7 @@
         <v>137176994</v>
       </c>
       <c r="B35" t="n">
-        <v>43525</v>
+        <v>43526</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4642,7 +4642,7 @@
         <v>137177000</v>
       </c>
       <c r="B36" t="n">
-        <v>43525</v>
+        <v>43526</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
